--- a/generation_zy/sowo-任务1-1.xlsx
+++ b/generation_zy/sowo-任务1-1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="15">
   <si>
     <t>PointX</t>
   </si>
@@ -45,13 +45,19 @@
     <t>PlaterName</t>
   </si>
   <si>
-    <t>Nc1ccccc1</t>
-  </si>
-  <si>
-    <t>20260924-001</t>
-  </si>
-  <si>
-    <t>96孔</t>
+    <t>ClC1=NC=CC=N1</t>
+  </si>
+  <si>
+    <t>20260922-001</t>
+  </si>
+  <si>
+    <t>96-1ml(AUT)</t>
+  </si>
+  <si>
+    <t>K2CO3</t>
+  </si>
+  <si>
+    <t>20261012-001</t>
   </si>
   <si>
     <t>Evaluation Only. Created with Aspose.Cells for Python via .NET. Copyright 2003 - 2026 Aspose Pty Ltd.</t>
@@ -517,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultColWidth="9.42428571428571" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9" ht="15">
@@ -563,7 +569,7 @@
         <v>9</v>
       </c>
       <c r="E2">
-        <v>93.099999999999994</v>
+        <v>5.70</v>
       </c>
       <c r="F2">
         <v>0.50</v>
@@ -576,6 +582,396 @@
       </c>
       <c r="I2" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3">
+        <v>5.70</v>
+      </c>
+      <c r="F3">
+        <v>0.50</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4">
+        <v>5.70</v>
+      </c>
+      <c r="F4">
+        <v>0.50</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5">
+        <v>5.70</v>
+      </c>
+      <c r="F5">
+        <v>0.50</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>5.70</v>
+      </c>
+      <c r="F6">
+        <v>0.50</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7">
+        <v>5.70</v>
+      </c>
+      <c r="F7">
+        <v>0.50</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8">
+        <v>5.70</v>
+      </c>
+      <c r="F8">
+        <v>0.50</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9">
+        <v>5.70</v>
+      </c>
+      <c r="F9">
+        <v>0.50</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10">
+        <v>11.10</v>
+      </c>
+      <c r="F10">
+        <v>0.50</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11">
+        <v>11.10</v>
+      </c>
+      <c r="F11">
+        <v>0.50</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12">
+        <v>11.10</v>
+      </c>
+      <c r="F12">
+        <v>0.50</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13">
+        <v>11.10</v>
+      </c>
+      <c r="F13">
+        <v>0.50</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14">
+        <v>11.10</v>
+      </c>
+      <c r="F14">
+        <v>0.50</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15">
+        <v>11.10</v>
+      </c>
+      <c r="F15">
+        <v>0.50</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16">
+        <v>11.10</v>
+      </c>
+      <c r="F16">
+        <v>0.50</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17">
+        <v>11.10</v>
+      </c>
+      <c r="F17">
+        <v>0.50</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -584,13 +980,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C68E47BE-0870-4DF0-9253-DB3F4AF5BAA4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9320717F-1506-4524-9A6F-C172116ABAA4}">
   <dimension ref="A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="5" spans="1:1" ht="23.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
